--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -546,6 +546,85 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0102002825</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1020100862210</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>МБОУ "НОШ-ДС №18" С. ВЕРХНЕНАЗАРОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "НАЧАЛЬНАЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА - ДЕТСКИЙ САД №18" С. ВЕРХНЕНАЗАРОВСКОЕ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>385334, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. ВЕРХНЕНАЗАРОВСКОЕ, УЛ. ПОЧТОВАЯ, Д. 53</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>385334</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>С. ВЕРХНЕНАЗАРОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Руководитель ликвидационной комиссии</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Терещенко Яна Байзетовна</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>85.12</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Образование начальное общее</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -625,6 +625,89 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0100007592</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>010001001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1240100000414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 28 ИМ. ГЕРОЯ РФ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 28 ИМЕНИ ГЕРОЯ РОССИЙСКОЙ ФЕДЕРАЦИИ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>385141, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, Г.П. ЯБЛОНОВСКОЕ, ПГТ. ЯБЛОНОВСКИЙ, УЛ. ИМЕНИ ВАЛЕРИЯ ИВАНОВИЧА ЗАВОЛЯНСКОГО, Д. 7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>385141</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Г.П. ЯБЛОНОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Барчо Сара Хамедовна</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -628,7 +628,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0100007592</t>
+          <t>0100009127</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -638,27 +638,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1240100000414</t>
+          <t>1240100001954</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>МБОУ "СШ № 28 ИМ. ГЕРОЯ РФ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ</t>
+          <t>МБОУ "СШ № 29" А. НОВАЯ АДЫГЕЯ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 28 ИМЕНИ ГЕРОЯ РОССИЙСКОЙ ФЕДЕРАЦИИ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 29" А. НОВАЯ АДЫГЕЯ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>385141, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, Г.П. ЯБЛОНОВСКОЕ, ПГТ. ЯБЛОНОВСКИЙ, УЛ. ИМЕНИ ВАЛЕРИЯ ИВАНОВИЧА ЗАВОЛЯНСКОГО, Д. 7</t>
+          <t>385142, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, С.П. СТАРОБЖЕГОКАЙСКОЕ, П. НОВАЯ АДЫГЕЯ, УЛ. БЖЕДУГСКАЯ, СТР. 12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>385141</t>
+          <t>385142</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -667,14 +667,10 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Г.П. ЯБЛОНОВСКОЕ</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ПГТ. ЯБЛОНОВСКИЙ</t>
+          <t>С.П. СТАРОБЖЕГОКАЙСКОЕ</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -687,7 +683,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Барчо Сара Хамедовна</t>
+          <t>Ермоленко Оксана Аскеровна</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -703,6 +699,89 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0100007592</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>010001001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1240100000414</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 28 ИМ. ГЕРОЯ РФ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 28 ИМЕНИ ГЕРОЯ РОССИЙСКОЙ ФЕДЕРАЦИИ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>385141, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, Г.П. ЯБЛОНОВСКОЕ, ПГТ. ЯБЛОНОВСКИЙ, УЛ. ИМЕНИ ВАЛЕРИЯ ИВАНОВИЧА ЗАВОЛЯНСКОГО, Д. 7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>385141</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Г.П. ЯБЛОНОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Барчо Сара Хамедовна</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>действующая</t>
         </is>

--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -707,7 +707,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0100007592</t>
+          <t>0100011670</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -717,27 +717,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1240100000414</t>
+          <t>1250100000700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>МБОУ "СШ № 28 ИМ. ГЕРОЯ РФ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ</t>
+          <t>МБОУ "СШ № 1 ИМ. Р. С. ТОРОХОВА"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 28 ИМЕНИ ГЕРОЯ РОССИЙСКОЙ ФЕДЕРАЦИИ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 1 ИМ. РОМАНА СЕРГЕЕВИЧА ТОРОХОВА"</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>385141, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, Г.П. ЯБЛОНОВСКОЕ, ПГТ. ЯБЛОНОВСКИЙ, УЛ. ИМЕНИ ВАЛЕРИЯ ИВАНОВИЧА ЗАВОЛЯНСКОГО, Д. 7</t>
+          <t>385019, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г.О. ГОРОД МАЙКОП, Г. МАЙКОП, УЛ. МИХАЙЛОВА, Д. 12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>385141</t>
+          <t>385019</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -748,14 +748,10 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Г.П. ЯБЛОНОВСКОЕ</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ПГТ. ЯБЛОНОВСКИЙ</t>
-        </is>
-      </c>
+          <t>Г.О. ГОРОД МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -766,7 +762,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Барчо Сара Хамедовна</t>
+          <t>Романенко Ольга Вячеславовна</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -782,6 +778,89 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0100007592</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>010001001</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1240100000414</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 28 ИМ. ГЕРОЯ РФ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 28 ИМЕНИ ГЕРОЯ РОССИЙСКОЙ ФЕДЕРАЦИИ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>385141, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, Г.П. ЯБЛОНОВСКОЕ, ПГТ. ЯБЛОНОВСКИЙ, УЛ. ИМЕНИ ВАЛЕРИЯ ИВАНОВИЧА ЗАВОЛЯНСКОГО, Д. 7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>385141</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Г.П. ЯБЛОНОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Барчо Сара Хамедовна</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>действующая</t>
         </is>

--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -866,6 +866,89 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0100012232</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>010001001</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1250100001260</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 30" ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 30" ПГТ. ЯБЛОНОВСКИЙ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>385140, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, Г.П. ЯБЛОНОВСКОЕ, ПГТ. ЯБЛОНОВСКИЙ, УЛ. ЗАВОДСКАЯ, Д. 21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>385140</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Г.П. ЯБЛОНОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Кайшев Георгий Александрович</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/schools.xlsx
+++ b/data/schools.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0102002825</t>
+          <t>0102001765</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -559,27 +559,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1020100862210</t>
+          <t>1020100862220</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>МБОУ "НОШ-ДС №18" С. ВЕРХНЕНАЗАРОВСКОЕ</t>
+          <t>"ШКОЛА-ИНТЕРНАТ ДЛЯ ДЕТЕЙ С ОВЗ"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "НАЧАЛЬНАЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА - ДЕТСКИЙ САД №18" С. ВЕРХНЕНАЗАРОВСКОЕ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+          <t>ГОСУДАРСТВЕННОЕ КАЗЕННОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ РЕСПУБЛИКИ АДЫГЕЯ "ШКОЛА-ИНТЕРНАТ ДЛЯ ДЕТЕЙ С ОГРАНИЧЕННЫМИ ВОЗМОЖНОСТЯМИ ЗДОРОВЬЯ"</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>385334, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. ВЕРХНЕНАЗАРОВСКОЕ, УЛ. ПОЧТОВАЯ, Д. 53</t>
+          <t>385440, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ШОВГЕНОВСКИЙ, АУЛ ХАКУРИНОХАБЛЬ, УЛ КРАСНООКТЯБРЬСКАЯ, ВЛД. 104</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>385334</t>
+          <t>385440</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -591,7 +591,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>С. ВЕРХНЕНАЗАРОВСКОЕ</t>
+          <t>АУЛ ХАКУРИНОХАБЛЬ</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -599,24 +599,24 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Руководитель ликвидационной комиссии</t>
+          <t>Директор</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Терещенко Яна Байзетовна</t>
+          <t>Хуажева Мариет Валериевна</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>85.12</t>
+          <t>85.13</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Образование начальное общее</t>
+          <t>Образование основное общее</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -628,37 +628,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0100009127</t>
+          <t>0102002127</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>010001001</t>
+          <t>010101001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1240100001954</t>
+          <t>1020100862209</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>МБОУ "СШ № 29" А. НОВАЯ АДЫГЕЯ</t>
+          <t>МБОУ "ГИМНАЗИЯ №1"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 29" А. НОВАЯ АДЫГЕЯ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ " ГИМНАЗИЯ № 1" С. КРАСНОГВАРДЕЙСКОГО КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>385142, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, С.П. СТАРОБЖЕГОКАЙСКОЕ, П. НОВАЯ АДЫГЕЯ, УЛ. БЖЕДУГСКАЯ, СТР. 12</t>
+          <t>385300, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. КРАСНОГВАРДЕЙСКОЕ, УЛ. ЧАПАЕВА, Д. 87А</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>385142</t>
+          <t>385300</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -670,7 +670,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>С.П. СТАРОБЖЕГОКАЙСКОЕ</t>
+          <t>С. КРАСНОГВАРДЕЙСКОЕ</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ермоленко Оксана Аскеровна</t>
+          <t>Ляшенко Ирина Ивановна</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -707,37 +707,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0100011670</t>
+          <t>0102002825</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>010001001</t>
+          <t>010101001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1250100000700</t>
+          <t>1020100862210</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>МБОУ "СШ № 1 ИМ. Р. С. ТОРОХОВА"</t>
+          <t>МБОУ "НОШ-ДС №18" С. ВЕРХНЕНАЗАРОВСКОЕ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 1 ИМ. РОМАНА СЕРГЕЕВИЧА ТОРОХОВА"</t>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "НАЧАЛЬНАЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА - ДЕТСКИЙ САД №18" С. ВЕРХНЕНАЗАРОВСКОЕ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>385019, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г.О. ГОРОД МАЙКОП, Г. МАЙКОП, УЛ. МИХАЙЛОВА, Д. 12</t>
+          <t>385334, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. ВЕРХНЕНАЗАРОВСКОЕ, УЛ. ПОЧТОВАЯ, Д. 53</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>385019</t>
+          <t>385334</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -746,35 +746,35 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Г.О. ГОРОД МАЙКОП</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>С. ВЕРХНЕНАЗАРОВСКОЕ</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Директор</t>
+          <t>Руководитель ликвидационной комиссии</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Романенко Ольга Вячеславовна</t>
+          <t>Терещенко Яна Байзетовна</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>85.12</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Образование среднее общее</t>
+          <t>Образование начальное общее</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -786,37 +786,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0100007592</t>
+          <t>0102004156</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>010001001</t>
+          <t>010101001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1240100000414</t>
+          <t>1020100861989</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>МБОУ "СШ № 28 ИМ. ГЕРОЯ РФ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ</t>
+          <t>МБОУ "ООШ № 10" С. ШТУРБИНО</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 28 ИМЕНИ ГЕРОЯ РОССИЙСКОЙ ФЕДЕРАЦИИ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "ОСНОВНАЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 10" С. ШТУРБИНО КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>385141, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, Г.П. ЯБЛОНОВСКОЕ, ПГТ. ЯБЛОНОВСКИЙ, УЛ. ИМЕНИ ВАЛЕРИЯ ИВАНОВИЧА ЗАВОЛЯНСКОГО, Д. 7</t>
+          <t>385325, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. ШТУРБИНО, УЛ. КРАСНАЯ, Д. 16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>385141</t>
+          <t>385325</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -825,14 +825,10 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Г.П. ЯБЛОНОВСКОЕ</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ПГТ. ЯБЛОНОВСКИЙ</t>
+          <t>С. ШТУРБИНО</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -845,19 +841,19 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Барчо Сара Хамедовна</t>
+          <t>Мерчанова Луиза Валеровна</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>85.13</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Образование среднее общее</t>
+          <t>Образование основное общее</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -869,37 +865,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0100012232</t>
+          <t>0102002631</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>010001001</t>
+          <t>010101001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1250100001260</t>
+          <t>1020100861725</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>МБОУ "СШ № 30" ПГТ. ЯБЛОНОВСКИЙ</t>
+          <t>МБОУ "ООШ № 12" ИМЕНИ Н.А.БЕРЗЕГОВА А.БЖЕДУГХАБЛЬ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 30" ПГТ. ЯБЛОНОВСКИЙ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "ОСНОВНАЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 12" ИМЕНИ Н.А.БЕРЗЕГОВА А.БЖЕДУГХАБЛЬ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>385140, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, Г.П. ЯБЛОНОВСКОЕ, ПГТ. ЯБЛОНОВСКИЙ, УЛ. ЗАВОДСКАЯ, Д. 21</t>
+          <t>385327, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, АУЛ БЖЕДУГХАБЛЬ, УЛ. ШКОЛЬНАЯ, Д. 1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>385140</t>
+          <t>385327</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -908,14 +904,10 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Г.П. ЯБЛОНОВСКОЕ</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ПГТ. ЯБЛОНОВСКИЙ</t>
+          <t>АУЛ БЖЕДУГХАБЛЬ</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -923,27 +915,5826 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Директор</t>
+          <t>Исполняющая обязанности директора</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Кайшев Георгий Александрович</t>
+          <t>Тугуз Зарема Аслановна</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
+          <t>85.13</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Образование основное общее</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0102004011</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1020100861890</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>МБОУ "ООШ №13" С. НОВОСЕВАСТОПОЛЬСКОЕ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ " ОСНОВНАЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №13" С. НОВОСЕВАСТОПОЛЬСКОЕ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>385332, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. НОВОСЕВАСТОПОЛЬСКОЕ, УЛ. ЧУЧВАГИ, Д. 4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>385332</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>С. НОВОСЕВАСТОПОЛЬСКОЕ</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Исполняющий обязанности директора</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Филоненко Ирина Владимировна</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>85.13</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Образование основное общее</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0102002744</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1020100861362</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>МБОУ "ООШ №14" С. ПРЕОБРАЖЕНСКОЕ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "ОСНОВНАЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 14" С.ПРЕОБРАЖЕНСКОЕ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>385330, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. ПРЕОБРАЖЕНСКОЕ, УЛ. ШКОЛЬНАЯ, Д. 30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>385330</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>С. ПРЕОБРАЖЕНСКОЕ</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Тхитлянов Рустам Схатбиевич</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>85.13</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Образование основное общее</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0102004082</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1020100861692</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>МБОУ "СОШ № 11" С. КРАСНОГВАРДЕЙСКОЕ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 11" С. КРАСНОГВАРДЕЙСКОЕ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>385301, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. КРАСНОГВАРДЕЙСКОЕ, УЛ. МИРА, ВЛД. 341</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>385301</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>С. КРАСНОГВАРДЕЙСКОЕ</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Быканова Людмила Александровна</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>85.14</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Образование среднее общее</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0102002663</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1020100862044</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>МБОУ "СОШ № 5" С. САДОВОЕ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 5" С. САДОВОЕ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>385333, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. САДОВОЕ, УЛ. КРАСНАЯ, Д. 14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>385333</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>С. САДОВОЕ</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Косенко Оксана Александровна</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0102004117</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1020100862000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>МБОУ "СОШ № 7" А. ДЖАМБЕЧИЙ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 7" А. ДЖАМБЕЧИЙ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>385329, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, АУЛ ДЖАМБЕЧИЙ, УЛ. ЦЕНТРАЛЬНАЯ, Д.31</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>385329</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>АУЛ ДЖАМБЕЧИЙ</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Директор школы</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Тлишева Люся Нурбиевна</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0101012919</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1180105002890</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>МБОУ "СОШ №10" Х.ХАПАЧЁВ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №10" Х.ХАПАЧЁВ ШОВГЕНОВСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>385443, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ШОВГЕНОВСКИЙ, Х ХАПАЧЕВ, УЛ КРАСНООКТЯБРЬСКАЯ, Д. 5А</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>385443</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Х ХАПАЧЕВ</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Хакуринова Сусанна Махаметовна</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0102004124</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1020100862011</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>МБОУ "СОШ №15" С. ЕЛЕНОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №15" ИМ. ГЕРОЯ РОССИИ Н.Н.ШЕВЕЛЕВА С.ЕЛЕНОВСКОЕ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>385322, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. ЕЛЕНОВСКОЕ, УЛ. МОЛОДЕЖНАЯ, ВЛД. 1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>385322</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>С. ЕЛЕНОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Зоболева Евгения Демьяновна</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0102003272</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1020100861670</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>МБОУ "СОШ №2" А. ХАТУКАЙ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 2 ИМ. Ю.К.ШХАЧЕМУКОВА" А.ХАТУКАЙ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>385321, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, АУЛ ХАТУКАЙ, УЛ. ШКОЛЬНАЯ, Д. 1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>385321</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>АУЛ ХАТУКАЙ</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Хапаева Майя Шалиховна</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0102004149</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1020100861329</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>МБОУ "СОШ №4" С. БЕЛОЕ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №4" ИМЕНИ СУШКИНА Т.Г. С. БЕЛОЕ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>385331, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. БЕЛОЕ, УЛ. СОВЕТСКАЯ, Д. 12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>385331</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>С. БЕЛОЕ</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Бельмехова Ирина Георгиевна</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0102004100</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1020100864178</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>МБОУ "СОШ №6" С. ЕЛЕНОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 6" С. ЕЛЕНОВСКОЕ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>385322, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С ЕЛЕНОВСКОЕ, УЛ ЮБИЛЕЙНАЯ, ВЛД. 23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>385322</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>С ЕЛЕНОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Атажахова Майя Кацовна</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0102004036</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1020100861923</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>МБОУ "СОШ №8" С. БОЛЬШЕСИДОРОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №8" С.БОЛЬШЕСИДОРОВСКОЕ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>385324, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, С. БОЛЬШЕСИДОРОВСКОЕ, УЛ. ШКОЛЬНАЯ, Д. 2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>385324</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>С. БОЛЬШЕСИДОРОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Такахо Сафер Шумафович</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0102002430</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1020100861758</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>МБОУ "СОШ №9" А. УЛЯП</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 9" А.УЛЯП КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>385326, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, АУЛ УЛЯП, УЛ. ИМ А.МУКОВА, Д. 67</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>385326</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>АУЛ УЛЯП</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Хаджуов Азамат Джумальдинович</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0100009127</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>010001001</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1240100001954</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 29" А. НОВАЯ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 29" А. НОВАЯ АДЫГЕЯ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>385142, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, С.П. СТАРОБЖЕГОКАЙСКОЕ, П. НОВАЯ АДЫГЕЯ, УЛ. БЖЕДУГСКАЯ, СТР. 12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>385142</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>С.П. СТАРОБЖЕГОКАЙСКОЕ</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ермоленко Оксана Аскеровна</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0106003428</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>010701001</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1020100825799</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 7 ИМ. ГЕРОЯ СОВЕТСКОГО СОЮЗА А. Б. ЧУЦА" А. ПАНАХЕС</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 7 ИМЕНИ ГЕРОЯ СОВЕТСКОГО СОЮЗА А. Б. ЧУЦА" АУЛА ПАНАХЕС ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>385113, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ТАХТАМУКАЙСКИЙ, АУЛ ПАНАХЕС, УЛ. СХАКУМИДОВА, ДВЛД. 1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>385113</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>АУЛ ПАНАХЕС</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Мамхо Лариса Баричевна</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0103002560</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1020100511177</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>МБОУ ООШ № 13</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН""ОСНОВНАЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 13"</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>385437, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н КОШЕХАБЛЬСКИЙ, С.П. ВОЛЬНЕНСКОЕ, Х. КАРМОЛИНО-ГИДРОИЦКИЙ, УЛ. СВОБОДЫ МИРА, Д. 121А</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>385437</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>С.П. ВОЛЬНЕНСКОЕ</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Василенко Светлана Евгеньевна</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>85.13</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Образование основное общее</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0103002779</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1020100509956</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>МБОУ ООШ №12</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН" "ОСНОВНАЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 12"</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>385435, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, Х. КАЗЕННО-КУЖОРСКИЙ, УЛ. ЛЕНИНА, Д. 50</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>385435</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Х. КАЗЕННО-КУЖОРСКИЙ</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Симоненко Любовь Павловна</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>85.13</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Образование основное общее</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0103001969</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1020100510319</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН""СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 1"</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>385400, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, АУЛ КОШЕХАБЛЬ, УЛ. ГАГАРИНА, Д. 53</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>385400</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>АУЛ КОШЕХАБЛЬ</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Адамиев Аслан Амербиевич</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0101004146</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1020100509780</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 1 ИМЕНИ А.Г. САПРУНОВА</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 1 ИМЕНИ А.Г. САПРУНОВА"</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>385600, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, СТ-ЦА ГИАГИНСКАЯ, УЛ ЛЕНИНА, Д. 152</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>385600</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>СТ-ЦА ГИАГИНСКАЯ</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Воробьева Елена Владимировна</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0103002610</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1020100511078</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 10</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН""СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 10"</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>385430, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, Х. ИГНАТЬЕВСКИЙ, УЛ. ЛЕНИНА, ВЛД. 92</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>385430</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Х. ИГНАТЬЕВСКИЙ</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Хупсарокова Зуриет Мухамедовна</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0101004273</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1020100509770</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 10 ИМ. Ф.И. АНТОНЦА</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 10 ИМЕНИ Ф.И. АНТОНЦА"</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>385635, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, СТ-ЦА ДОНДУКОВСКАЯ, УЛ. ЛЕНИНА, ВЛД. 73</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>385635</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>СТ-ЦА ДОНДУКОВСКАЯ</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Слободчикова Наталья Ивановна</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0101004241</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1020100509747</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 11</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 11"</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>385637, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, С. СЕРГИЕВСКОЕ, УЛ. ВЫГОННАЯ, Д. 46</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>385637</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>С. СЕРГИЕВСКОЕ</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Кихтева Светлана Михайловна</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0103001951</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1020100507921</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН""СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 2"</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>385400, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, АУЛ КОШЕХАБЛЬ, УЛ. ДЖАРИМОВА А., Д.4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>385400</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>АУЛ КОШЕХАБЛЬ</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Беджанов Юрий Борисович</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0103002553</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1020100511155</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН" "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 4"</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>385423, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, АУЛ ХАЧЕМЗИЙ, УЛ. ЛЕНИНА, Д. 41</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>385423</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>АУЛ ХАЧЕМЗИЙ</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Эльдаров Инвер Нальбиевич</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0103002803</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1020100510385</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 5 ИМ. ГЕРОЯ СОВЕТСКОГО СОЮЗА А.Ю. КОШЕВА</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН" "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 5 ИМЕНИ ГЕРОЯ СОВЕТСКОГО СОЮЗА АЛИЯ ЮСУФОВИЧА КОШЕВА"</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>385431, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, АУЛ БЛЕЧЕПСИН, УЛ. КОШЕВА, Д. 4</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>385431</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>АУЛ БЛЕЧЕПСИН</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Мекулова Марьят Хусейновна</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0101004160</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1020100509725</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 6</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 6"</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>385631, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, П. ГОНЧАРКА, УЛ. ГИАГИНСКАЯ, Д. 1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>385631</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>П. ГОНЧАРКА</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Тютерева Галина Николаевна</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0103002546</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1020100509990</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 6</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН""СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 6"</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>385424, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, П. ДРУЖБА, УЛ. ШКОЛЬНАЯ, ВЛД. 1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>385424</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>П. ДРУЖБА</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Берзегова Элла Юриевна</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0103002786</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1020100510352</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 7</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН""СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №7"</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>385433, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, П. МАЙСКИЙ, УЛ. ФИЛАТОВА, ВЛД. 5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>385433</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>П. МАЙСКИЙ</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Шаматрина Нина Николаевна</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0103002592</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1020100509967</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 8</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН" "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 8"</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>385434, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, С. НАТЫРБОВО, УЛ. КРАСНАЯ, ВЛД. 45</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>385434</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>С. НАТЫРБОВО</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Мамишев Эдуард Асланович</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0101004153</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1020100507173</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 9</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 9"</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>385635, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, СТ-ЦА ДОНДУКОВСКАЯ, УЛ. ГАГАРИНА, ВЛД. 148</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>385635</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>СТ-ЦА ДОНДУКОВСКАЯ</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Шаповалова Татьяна Борисовна</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0103002585</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1020100511551</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ № 9</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН""СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА № 9"</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>385436, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, С. ВОЛЬНОЕ, УЛ. ЛЕНИНА, Д. 154</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>385436</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>С. ВОЛЬНОЕ</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Директор школы</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Мамишев Руслан Асланович</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0103002754</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1020100510847</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ №11</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН""СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №11"</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>385438, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, АУЛ ХОДЗЬ, УЛ. КРАСНООКТЯБРЬСКАЯ, Д. 101</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>385438</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>АУЛ ХОДЗЬ</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Афашагова Ирма Аскарбиевна</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0101004185</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1020100508658</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ №12</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №12"</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>385638, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, Х. ТАМБОВСКИЙ, УЛ. ПРЯМАЯ, Д. 30</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>385638</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Х. ТАМБОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Мокротоварова Оксана Викторовна</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0101004202</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1020100509802</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ №2 ИМ. А.АСЕЕВА И Ю.ГОЛИКОВА</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №2 ИМЕНИ А.АСЕЕВА И Ю.ГОЛИКОВА"</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>385601, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, СТ-ЦА ГИАГИНСКАЯ, УЛ ЦЕНТРАЛЬНАЯ, Д. 38</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>385601</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>СТ-ЦА ГИАГИНСКАЯ</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Порецкая Ольга Николаевна</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0101004192</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1020100507129</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ №3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №3"</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>385600, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, СТ-ЦА ГИАГИНСКАЯ, УЛ БОЕВАЯ, Д. 3</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>385600</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>СТ-ЦА ГИАГИНСКАЯ</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Слюсарев Николай Викторович</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0102004075</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1020100861736</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ №3 А. АДАМИЙ</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №3" ИМ. М.И. КУДАЕВА А. АДАМИЙ КРАСНОГВАРДЕЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>385336, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КРАСНОГВАРДЕЙСКИЙ, АУЛ АДАМИЙ, 50 ЛЕТ ОКТЯБРЯ, Д.50</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>385336</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>АУЛ АДАМИЙ</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Цеева Людмила Аскарбиевна</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0103002578</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1020100511243</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ №3 ИМ. ПЕРВОГО ПРЕЗИДЕНТА РЕСПУБЛИКИ АДЫГЕЯ ДЖАРИМОВА А.А.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ МУНИЦИПАЛЬНОГО ОБРАЗОВАНИЯ "КОШЕХАБЛЬСКИЙ РАЙОН" "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №3 ИМЕНИ ПЕРВОГО ПРЕЗИДЕНТА РЕСПУБЛИКИ АДЫГЕЯ ДЖАРИМОВА АСЛАНА АЛИЕВИЧА"</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>385421, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н КОШЕХАБЛЬСКИЙ, АУЛ ЕГЕРУХАЙ, УЛ. ШКОЛЬНАЯ, Д. 28А</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>385421</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>АУЛ ЕГЕРУХАЙ</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Хасанова Саида Юрьевна</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0101004266</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1020100509758</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ №4</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №4"</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>385600, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, СТ-ЦА ГИАГИНСКАЯ, УЛ КРАСНАЯ, Д. 170</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>385600</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>СТ-ЦА ГИАГИНСКАЯ</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Пугачев Дмитрий Филиппович</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0101004210</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1020100508163</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ №5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №5 "</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>385634, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, Х. ПРОГРЕСС, УЛ. ЦЕНТРАЛЬНАЯ, Д. 2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>385634</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Х. ПРОГРЕСС</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Губарева Елена Владимировна</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0101004259</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1020100509769</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ №7</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №7"</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>385633, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, П. НОВЫЙ, УЛ. ШКОЛЬНАЯ, ВЛД. 22</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>385633</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>П. НОВЫЙ</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Качанова Оксана Владимировна</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0101003488</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>010101001</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1020100507602</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>МБОУ СОШ №8 ИМ. В.СОЛДАТЕНКО</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ГИАГИНСКОГО РАЙОНА "СРЕДНЯЯ ОБЩЕОБРАЗОВАТЕЛЬНАЯ ШКОЛА №8 ИМЕНИ В.СОЛДАТЕНКО"</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>385632, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Р-Н ГИАГИНСКИЙ, СТ-ЦА КЕЛЕРМЕССКАЯ, УЛ. СОВЕТСКАЯ, ВЛД. 116</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>385632</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>СТ-ЦА КЕЛЕРМЕССКАЯ</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Усольцева Наталья Васильевна</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0105033444</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1020100700124</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ГБОУ "АДЫГЕЙСКАЯ РЕСПУБЛИКАНСКАЯ ГИМНАЗИЯ"</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ РЕСПУБЛИКИ АДЫГЕЯ "АДЫГЕЙСКАЯ РЕСПУБЛИКАНСКАЯ ГИМНАЗИЯ"</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>385000, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. СОВЕТСКАЯ, Д. 241</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>385000</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Чич Нуриет Шамсудиновна</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0105033490</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1020100711729</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ГКОУ РА "АРШИДНСИЗ"</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННОЕ КАЗЕННОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ РЕСПУБЛИКИ АДЫГЕЯ "АДЫГЕЙСКАЯ РЕСПУБЛИКАНСКАЯ ШКОЛА-ИНТЕРНАТ ДЛЯ ДЕТЕЙ С НАРУШЕНИЯМИ СЛУХА И ЗРЕНИЯ"</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>385017, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. КРЫЛОВА 2-Я, Д.2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>385017</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Чумаков Роман Николаевич</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0105043682</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1040100551336</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ГКОУ РА "ШКОЛА ДЛЯ ДЕТЕЙ С ОГРАНИЧЕННЫМИ ВОЗМОЖНОСТЯМИ ЗДОРОВЬЯ"</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННОЕ КАЗЕННОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ РЕСПУБЛИКИ АДЫГЕЯ "ШКОЛА ДЛЯ ДЕТЕЙ С ОГРАНИЧЕННЫМИ ВОЗМОЖНОСТЯМИ ЗДОРОВЬЯ"</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>385002, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. 12 МАРТА, Д. 65</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>385002</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Нестеренко Ирина Евгеньевна</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>85.13</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Образование основное общее</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0105032151</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1020100709309</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>МБОУ "ЛИЦЕЙ № 8"</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "ЛИЦЕЙ № 8 ИМЕНИ ЖЕНИ ПОПОВА"</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>385006, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. ГОГОЛЯ, Д.112</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>385006</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Осерская Эмма Владимировна</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0105032144</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1020100708924</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>МБОУ "ЛИЦЕЙ № 19"</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "ЛИЦЕЙ № 19"</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>385000, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. КРАСНООКТЯБРЬСКАЯ, Д. 51</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>385000</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Исполняющая обязанности директора</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Кадырова Фатима Юрьевна</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0105037255</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1020100709650</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>МБОУ "ЛИЦЕЙ № 35"</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "ЭКОЛОГО- БИОЛОГИЧЕСКИЙ ЛИЦЕЙ № 35"</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>385018, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. ПИОНЕРСКАЯ, Д. 532</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>385018</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Эйхвальд Анастасия Романовна</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0105033451</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1020100708561</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>МБОУ "МАЙКОПСКАЯ ГИМНАЗИЯ № 22"</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "МАЙКОПСКАЯ ГИМНАЗИЯ № 22"</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>385018, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. ДЕПУТАТСКАЯ, Д. 10</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>385018</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Андреева Ирина Витальевна</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0105032049</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1020100708682</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>МБОУ "МАЙКОПСКАЯ ГИМНАЗИЯ № 5"</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "МАЙКОПСКАЯ ГИМНАЗИЯ № 5 ИМЕНИ ЕВГЕНИЯ ЛЬВОВИЧА ШВАРЦА"</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>385000, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. ПУШКИНА, Д. 173</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>385000</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Бородкина Надежда Григорьевна</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0105032017</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1020100708484</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>МБОУ "НШ № 26"</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "НАЧАЛЬНАЯ ШКОЛА № 26"</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>385060, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, СТ-ЦА ХАНСКАЯ, УЛ. ИНТЕРНАЦИОНАЛЬНАЯ, ДВЛД. 112</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>385060</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>СТ-ЦА ХАНСКАЯ</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Княжина Ирина Николаевна</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>85.12</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Образование начальное общее</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0105033934</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1020100709287</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>МБОУ "ОШ № 20"</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "ОСНОВНАЯ ШКОЛА № 20"</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>385002, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. МОПРА, ДВЛД. 65</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>385002</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Черная Людмила Александровна</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>85.13</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Образование основное общее</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0105032070</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1020100705844</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>МБОУ "ОШ № 24"</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "ОСНОВНАЯ ШКОЛА № 24"</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>385069, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, П. РОДНИКОВЫЙ, УЛ. ЛЕНИНА, Д. 14</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>385069</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>П. РОДНИКОВЫЙ</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Исполняющий обязанности директора</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Шаова Асият Зауровна</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>85.13</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Образование основное общее</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0105032779</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1020100708968</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>МБОУ "ОШ № 25"</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "ОСНОВНАЯ ШКОЛА № 25"</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>385060, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, СТ-ЦА ХАНСКАЯ, УЛ. ЛЕНИНА, Д. 36</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>385060</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>СТ-ЦА ХАНСКАЯ</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Комарова Ирина Валерьевна</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>85.13</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Образование основное общее</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0105033571</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1020100704931</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>МБОУ "ОШ № 27"</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "ОСНОВНАЯ ШКОЛА № 27"</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>385071, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, П. СЕВЕРНЫЙ, УЛ. ШКОЛЬНАЯ, ДВЛД. 1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>385071</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>П. СЕВЕРНЫЙ</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Трипкош Юлия Васильевна</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>85.13</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Образование основное общее</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0105031750</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1020100694900</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>МБОУ "СРЕДНЯЯ ШКОЛА № 3 ИМЕНИ АЛЕКСЕЯ ИОСИФОВИЧА МАКАРЕНКО"</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 3 ИМЕНИ АЛЕКСЕЯ ИОСИФОВИЧА МАКАРЕНКО"</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>385012, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. ТУЛЬСКАЯ, Д. 3</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>385012</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Пашкова Анна Руслановна</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0105032063</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1020100707054</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 10 ИМ. А. В. ГАРМАША"</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 10 ИМЕНИ АРТЕМА ВЛАДИМИРОВИЧА ГАРМАША"</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>385020, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. КУРГАННАЯ, Д. 644</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>385020</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Жаркова Наталья Андреевна</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0105032088</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1020100704876</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 11"</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 11"</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>385008, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. 12 МАРТА, Д. 144А</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>385008</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Исполняющий обязанности директора</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Кузнецова Виктория Геннадиевна</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0105033081</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1020100708143</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 13"</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 13"</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>385020, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. 8 МАРТА, ДВЛД. 21</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>385020</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Неверова Марина Владимировна</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0105033420</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1020100708473</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 14"</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 14"</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>385064, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, П. ПОДГОРНЫЙ, ПЕР. ШКОЛЬНЫЙ, Д. 12</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>385064</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>П. ПОДГОРНЫЙ</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Цишева Зулима Нурбиевна</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0105033324</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1020100710520</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 15"</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 15"</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>385007, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. КУРГАННАЯ, Д. 1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>385007</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Биштова Зурет Нурбиевна</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0105031863</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1020100706911</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 16"</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 16"</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>385003, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. КИРОВА, Д. 130</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>385003</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Шатилова Галина Анатольевна</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0105033282</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1020100708759</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 17"</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 17 СОЦИАЛЬНОГО РАЗВИТИЯ И УСПЕХА"</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>385019, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, ПЕР. 7-Й, Д. 22</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>385019</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Купин Олег Петрович</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0105032377</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1020100704953</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 2 ИМЕНИ ВАДИМА ЛЕМЕША"</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 2 ИМЕНИ ВАДИМА ВЯЧЕСЛАВОВИЧА ЛЕМЕША"</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>385008, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. 12 МАРТА, Д. 126</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>385008</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Басниева Саида Борисовна</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0105033010</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1020100705184</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 23 ИМ. А.П. АНТОНОВА"</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 23 ИМ. А.П. АНТОНОВА"</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>385060, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, СТ-ЦА ХАНСКАЯ, УЛ. КРАСНООКТЯБРЬСКАЯ, Д. 40</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>385060</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>СТ-ЦА ХАНСКАЯ</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Кузьменко Людмила Александровна</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0105032909</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1020100694954</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 28"</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 28"</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>385002, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. ГАЙДАРА, Д. 1А</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>385002</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Казаков Анатолий Павлович</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0105033902</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1020100709397</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 6"</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 6"</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>385002, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. КОМСОМОЛЬСКАЯ, Д. 276</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>385002</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Шевоцукова Марина Николаевна</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0105033074</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1020100709166</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 7"</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 7"</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>385020, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. КУРГАННАЯ, Д. 331</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>385020</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Обернинов Виталий Викторович</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0105031969</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1020100694910</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 9"</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 9"</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>385016, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. СОВЕТСКАЯ, Д. 108</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>385016</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Биржева Бэлла Муратовна</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0105029582</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1020100702160</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ЧУОО "ПРАВОСЛАВНАЯ ГИМНАЗИЯ"</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ЧАСТНОЕ УЧРЕЖДЕНИЕ "ОБЩЕОБРАЗОВАТЕЛЬНАЯ ОРГАНИЗАЦИЯ "ПРАВОСЛАВНАЯ ГИМНАЗИЯ ВО ИМЯ ПРЕПОДОБНОГО СЕРГИЯ РАДОНЕЖСКОГО"</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>385452, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г. МАЙКОП, УЛ. МОПРА, ДВЛД. 85</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>385452</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Г. МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Дьяченко Елена Александровна</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0105033250</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1020100694888</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>МБОУ "ЛИЦЕЙ № 34"</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "ЛИЦЕЙ № 34"</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>385008, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г.О. ГОРОД МАЙКОП, Г. МАЙКОП, УЛ. 12 МАРТА, Д. 164</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>385008</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Г.О. ГОРОД МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Мугу Бэла Руслановна</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0100011670</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>010001001</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1250100000700</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 1 ИМ. Р. С. ТОРОХОВА"</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 1 ИМ. РОМАНА СЕРГЕЕВИЧА ТОРОХОВА"</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>385019, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г.О. ГОРОД МАЙКОП, Г. МАЙКОП, УЛ. МИХАЙЛОВА, Д. 12</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>385019</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Г.О. ГОРОД МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Романенко Ольга Вячеславовна</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0105076751</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>010501001</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1160105051083</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ЧОУ ОО "ШКОЛА "ГЛОБУС"</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ЧАСТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ ОБЩЕГО ОБРАЗОВАНИЯ "ШКОЛА "ГЛОБУС"</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>385020, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), Г.О. ГОРОД МАЙКОП, Г. МАЙКОП, УЛ. ШКОЛЬНАЯ, Д. 166/1, КВ. 1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>385020</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Г.О. ГОРОД МАЙКОП</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Нарудьян Рубен Еревантович</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>85.12</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Образование начальное общее</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0100007592</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>010001001</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1240100000414</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 28 ИМ. ГЕРОЯ РФ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 28 ИМЕНИ ГЕРОЯ РОССИЙСКОЙ ФЕДЕРАЦИИ ЗАВОЛЯНСКОГО В.И." ПГТ. ЯБЛОНОВСКИЙ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>385141, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, Г.П. ЯБЛОНОВСКОЕ, ПГТ. ЯБЛОНОВСКИЙ, УЛ. ИМЕНИ ВАЛЕРИЯ ИВАНОВИЧА ЗАВОЛЯНСКОГО, Д. 7</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>385141</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Г.П. ЯБЛОНОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Барчо Сара Хамедовна</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>действующая</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0100012232</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>010001001</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1250100001260</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>МБОУ "СШ № 30" ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>МУНИЦИПАЛЬНОЕ БЮДЖЕТНОЕ ОБЩЕОБРАЗОВАТЕЛЬНОЕ УЧРЕЖДЕНИЕ "СРЕДНЯЯ ШКОЛА № 30" ПГТ. ЯБЛОНОВСКИЙ ТАХТАМУКАЙСКОГО РАЙОНА РЕСПУБЛИКИ АДЫГЕЯ</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>385140, РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ), М.Р-Н ТАХТАМУКАЙСКИЙ, Г.П. ЯБЛОНОВСКОЕ, ПГТ. ЯБЛОНОВСКИЙ, УЛ. ЗАВОДСКАЯ, Д. 21</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>385140</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>РЕСПУБЛИКА АДЫГЕЯ (АДЫГЕЯ)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Г.П. ЯБЛОНОВСКОЕ</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ПГТ. ЯБЛОНОВСКИЙ</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Директор</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Кайшев Георгий Александрович</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>85.14</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Образование среднее общее</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
         <is>
           <t>действующая</t>
         </is>
